--- a/data/baseline_results/summary_final.xlsx
+++ b/data/baseline_results/summary_final.xlsx
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="4">
@@ -591,16 +591,16 @@
         <v>0.448</v>
       </c>
       <c r="D7" t="n">
-        <v>0.648</v>
+        <v>0.661</v>
       </c>
       <c r="E7" t="n">
-        <v>0.696</v>
+        <v>0.704</v>
       </c>
       <c r="F7" t="n">
-        <v>0.721</v>
+        <v>0.733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.612</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="8">
